--- a/artifacts/review/知识图谱关系-修改.xlsx
+++ b/artifacts/review/知识图谱关系-修改.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23400" windowHeight="11655"/>
+    <workbookView windowWidth="28260" windowHeight="12160"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="2" r:id="rId1"/>
@@ -467,6 +467,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">沉淀温度
 </t>
     </r>
@@ -494,6 +501,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">干燥温度
 </t>
     </r>
@@ -513,6 +527,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">焙烧温度
 </t>
     </r>
@@ -538,6 +559,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">浸渍温度
 </t>
     </r>
@@ -553,6 +581,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>干燥温度</t>
     </r>
     <r>
@@ -574,6 +609,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">干燥时间
 </t>
     </r>
@@ -624,6 +666,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">温度
 </t>
     </r>
@@ -667,6 +716,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>耐热前
 375</t>
     </r>
@@ -682,6 +738,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>耐热前
 400</t>
     </r>
@@ -697,6 +760,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>耐热前
 425</t>
     </r>
@@ -712,6 +782,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>耐热前
 450</t>
     </r>
@@ -727,6 +804,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>耐热后
 375</t>
     </r>
@@ -742,6 +826,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>耐热后
 400</t>
     </r>
@@ -757,6 +848,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>耐热后
 425</t>
     </r>
@@ -772,6 +870,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>耐热后
 450</t>
     </r>
@@ -830,7 +935,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -843,13 +948,6 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1018,12 +1116,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -1369,137 +1461,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1515,20 +1607,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -1542,13 +1625,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1871,503 +1954,503 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C53"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.85" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9.02678571428571" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="9.02654867256637" style="10"/>
-    <col min="2" max="2" width="13.4336283185841" style="10" customWidth="1"/>
-    <col min="3" max="3" width="72.2920353982301" style="11" customWidth="1"/>
+    <col min="1" max="1" width="9.02678571428571" style="7"/>
+    <col min="2" max="2" width="13.4375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="124.401785714286" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:3">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="12" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="12" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="1:3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12" t="s">
+    <row r="12" ht="18" spans="1:3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="12" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12" t="s">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12" t="s">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12" t="s">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12" t="s">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="12" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12" t="s">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12" t="s">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="12" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12" t="s">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="12" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12" t="s">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12" t="s">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="12" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12" t="s">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="12" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12" t="s">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="12" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12" t="s">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="12" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12" t="s">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12" t="s">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="12" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12" t="s">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="12" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12" t="s">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="35" ht="13.9" spans="1:3">
-      <c r="A35" s="12"/>
+    <row r="35" ht="17" spans="1:3">
+      <c r="A35" s="9"/>
       <c r="B35" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="12" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12" t="s">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="12" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12" t="s">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="12" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12" t="s">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="12" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12" t="s">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="12"/>
-      <c r="B41" s="12" t="s">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="12" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12" t="s">
+      <c r="A42" s="9"/>
+      <c r="B42" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="12" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12" t="s">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="12" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12" t="s">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="12" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12" t="s">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12" t="s">
+      <c r="A46" s="9"/>
+      <c r="B46" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="12" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12" t="s">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="12" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="12"/>
-      <c r="B48" s="12" t="s">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="12" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="12" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="12"/>
-      <c r="B50" s="12" t="s">
+      <c r="A50" s="9"/>
+      <c r="B50" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="12" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12" t="s">
+      <c r="A51" s="9"/>
+      <c r="B51" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="12" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12" t="s">
+      <c r="A52" s="9"/>
+      <c r="B52" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="12" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12" t="s">
+      <c r="A53" s="9"/>
+      <c r="B53" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="12" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2390,24 +2473,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V9"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.85"/>
+  <sheetFormatPr defaultColWidth="9.02678571428571" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="8.31858407079646" customWidth="1"/>
-    <col min="2" max="2" width="4.51327433628319" customWidth="1"/>
-    <col min="3" max="3" width="8.31858407079646" customWidth="1"/>
-    <col min="4" max="4" width="4.51327433628319" customWidth="1"/>
-    <col min="5" max="5" width="8.31858407079646" customWidth="1"/>
-    <col min="6" max="6" width="4.51327433628319" customWidth="1"/>
-    <col min="7" max="7" width="8.31858407079646" customWidth="1"/>
-    <col min="8" max="8" width="4.51327433628319" customWidth="1"/>
-    <col min="9" max="9" width="8.31858407079646" customWidth="1"/>
-    <col min="10" max="10" width="4.51327433628319" customWidth="1"/>
-    <col min="11" max="11" width="6.44247787610619" customWidth="1"/>
-    <col min="12" max="12" width="10.2920353982301" customWidth="1"/>
-    <col min="13" max="13" width="6.44247787610619" customWidth="1"/>
-    <col min="14" max="15" width="8.36283185840708" customWidth="1"/>
-    <col min="16" max="16" width="10.8849557522124" customWidth="1"/>
-    <col min="17" max="22" width="8.36283185840708" customWidth="1"/>
+    <col min="1" max="1" width="8.32142857142857" customWidth="1"/>
+    <col min="2" max="2" width="4.50892857142857" customWidth="1"/>
+    <col min="3" max="3" width="8.32142857142857" customWidth="1"/>
+    <col min="4" max="4" width="4.50892857142857" customWidth="1"/>
+    <col min="5" max="5" width="8.32142857142857" customWidth="1"/>
+    <col min="6" max="6" width="4.50892857142857" customWidth="1"/>
+    <col min="7" max="7" width="8.32142857142857" customWidth="1"/>
+    <col min="8" max="8" width="4.50892857142857" customWidth="1"/>
+    <col min="9" max="9" width="8.32142857142857" customWidth="1"/>
+    <col min="10" max="10" width="4.50892857142857" customWidth="1"/>
+    <col min="11" max="11" width="6.44642857142857" customWidth="1"/>
+    <col min="12" max="12" width="10.2946428571429" customWidth="1"/>
+    <col min="13" max="13" width="6.44642857142857" customWidth="1"/>
+    <col min="14" max="15" width="8.36607142857143" customWidth="1"/>
+    <col min="16" max="16" width="10.8839285714286" customWidth="1"/>
+    <col min="17" max="22" width="8.36607142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -2436,7 +2519,7 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" ht="27.75" spans="1:22">
+    <row r="2" ht="51" spans="1:22">
       <c r="A2" s="5" t="s">
         <v>115</v>
       </c>
@@ -2479,7 +2562,7 @@
       <c r="N2" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="6" t="s">
         <v>125</v>
       </c>
       <c r="P2" s="6" t="s">
@@ -2491,13 +2574,13 @@
       <c r="R2" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="S2" s="6" t="s">
         <v>129</v>
       </c>
       <c r="T2" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="U2" s="6" t="s">
         <v>131</v>
       </c>
       <c r="V2" s="6" t="s">
@@ -2554,7 +2637,7 @@
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
     </row>
-    <row r="5" ht="27.75" spans="1:22">
+    <row r="5" ht="51" spans="1:19">
       <c r="A5" s="5" t="s">
         <v>115</v>
       </c>
@@ -2597,23 +2680,23 @@
       <c r="N5" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="P5" s="5" t="s">
         <v>136</v>
       </c>
       <c r="Q5" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="R5" s="6" t="s">
         <v>131</v>
       </c>
       <c r="S5" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:17">
       <c r="A7" s="5" t="s">
         <v>137</v>
       </c>
@@ -2634,7 +2717,7 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
     </row>
-    <row r="8" ht="27.75" spans="1:22">
+    <row r="8" ht="51" spans="1:17">
       <c r="A8" s="5" t="s">
         <v>115</v>
       </c>
@@ -2674,20 +2757,20 @@
       <c r="M8" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="O8" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="6" t="s">
         <v>131</v>
       </c>
       <c r="Q8" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:17">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -2721,7 +2804,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.85" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9.02678571428571" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -2798,7 +2881,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:X2"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.85" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9.02678571428571" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
@@ -2832,7 +2915,7 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
     </row>
-    <row r="2" ht="27.75" spans="1:24">
+    <row r="2" ht="34" spans="1:24">
       <c r="A2" s="2" t="s">
         <v>149</v>
       </c>
@@ -2921,7 +3004,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.85" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9.02678571428571" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
@@ -2943,7 +3026,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" ht="27.75" spans="1:16">
+    <row r="2" ht="34" spans="1:16">
       <c r="A2" s="2" t="s">
         <v>169</v>
       </c>
@@ -3006,7 +3089,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.85"/>
+  <sheetFormatPr defaultColWidth="9.02678571428571" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
